--- a/Mediciones/RNA/L/RUN1_L_2NO.xlsx
+++ b/Mediciones/RNA/L/RUN1_L_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\L\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C51AF9-5EE4-4FD7-BD23-FD121C769F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0CA7E2-5B9B-4DC6-B115-BA8301C11A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -548,6 +548,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T21:53:58",
   "bounds": {
@@ -558,7 +561,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -649,9 +652,6 @@
   "run_id": "R20260718_215358",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D2">
         <v>1.440706929039718E-2</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D3">
         <v>1.440706929039718E-2</v>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4">
         <v>1.440706929039718E-2</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D5">
         <v>1.440706929039718E-2</v>
@@ -1321,7 +1321,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6">
         <v>1.440706929039718E-2</v>
@@ -1374,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D7">
         <v>1.4748357299370971E-2</v>
@@ -1427,7 +1427,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D8">
         <v>1.4748357299370971E-2</v>
@@ -1480,7 +1480,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D9">
         <v>1.4748357299370971E-2</v>
@@ -1533,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10">
         <v>1.4748357299370971E-2</v>
@@ -1586,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D11">
         <v>1.4748357299370971E-2</v>
@@ -1639,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D12">
         <v>1.4748357299370971E-2</v>
@@ -1692,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13">
         <v>1.642947009142396E-2</v>
@@ -1745,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D14">
         <v>1.642947009142396E-2</v>
@@ -1798,7 +1798,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D15">
         <v>1.642947009142396E-2</v>
@@ -1851,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16">
         <v>1.642947009142396E-2</v>
@@ -1904,7 +1904,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D17">
         <v>1.642947009142396E-2</v>
@@ -1957,7 +1957,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D18">
         <v>1.642947009142396E-2</v>
@@ -2010,7 +2010,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19">
         <v>1.642947009142396E-2</v>
@@ -2063,7 +2063,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D20">
         <v>1.642947009142396E-2</v>
@@ -2116,7 +2116,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D21">
         <v>1.642947009142396E-2</v>
@@ -2169,7 +2169,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D22">
         <v>1.642947009142396E-2</v>
@@ -2222,7 +2222,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D23">
         <v>1.642947009142396E-2</v>
@@ -2275,7 +2275,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D24">
         <v>1.7427472726675639E-2</v>
@@ -2328,7 +2328,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D25">
         <v>1.7427472726675639E-2</v>
@@ -2381,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D26">
         <v>1.7427472726675639E-2</v>
@@ -2434,7 +2434,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D27">
         <v>1.7427472726675639E-2</v>
@@ -2487,7 +2487,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D28">
         <v>1.7427472726675639E-2</v>
@@ -2540,7 +2540,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D29">
         <v>1.7427472726675639E-2</v>
@@ -2593,7 +2593,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D30">
         <v>1.7427472726675639E-2</v>
@@ -2646,7 +2646,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D31">
         <v>1.7427472726675639E-2</v>
@@ -2699,7 +2699,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D32">
         <v>1.7427472726675639E-2</v>
@@ -2752,7 +2752,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D33">
         <v>1.7427472726675639E-2</v>
@@ -2805,7 +2805,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D34">
         <v>1.7427472726675639E-2</v>
@@ -2858,7 +2858,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D35">
         <v>1.7427472726675639E-2</v>
@@ -2911,7 +2911,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D36">
         <v>1.7427472726675639E-2</v>
@@ -2964,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D37">
         <v>1.7427472726675639E-2</v>
@@ -3017,7 +3017,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D38">
         <v>1.7427472726675639E-2</v>
@@ -3070,7 +3070,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39">
         <v>1.7427472726675639E-2</v>
@@ -3123,7 +3123,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D40">
         <v>1.7427472726675639E-2</v>
@@ -3176,7 +3176,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D41">
         <v>2.00700130350576E-2</v>
@@ -3229,7 +3229,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42">
         <v>2.00700130350576E-2</v>
@@ -3282,7 +3282,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D43">
         <v>2.00700130350576E-2</v>
@@ -3335,7 +3335,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44">
         <v>2.00700130350576E-2</v>
@@ -3388,7 +3388,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D45">
         <v>2.00700130350576E-2</v>
@@ -3441,7 +3441,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D46">
         <v>2.00700130350576E-2</v>
@@ -3494,7 +3494,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47">
         <v>2.00700130350576E-2</v>
@@ -3547,7 +3547,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D48">
         <v>2.00700130350576E-2</v>
@@ -3600,7 +3600,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D49">
         <v>2.00700130350576E-2</v>
@@ -3653,7 +3653,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50">
         <v>2.00700130350576E-2</v>
@@ -3706,7 +3706,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D51">
         <v>2.00700130350576E-2</v>
@@ -3759,7 +3759,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D52">
         <v>2.00700130350576E-2</v>
@@ -3812,7 +3812,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D53">
         <v>2.00700130350576E-2</v>
@@ -3865,7 +3865,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D54">
         <v>2.00700130350576E-2</v>
@@ -3918,7 +3918,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D55">
         <v>2.00700130350576E-2</v>
@@ -3971,7 +3971,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D56">
         <v>2.00700130350576E-2</v>
@@ -4024,7 +4024,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D57">
         <v>2.00700130350576E-2</v>
@@ -4077,7 +4077,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D58">
         <v>2.00700130350576E-2</v>
@@ -4130,7 +4130,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59">
         <v>2.0536732762728639E-2</v>
@@ -4183,7 +4183,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D60">
         <v>2.0536732762728639E-2</v>
@@ -4236,7 +4236,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D61">
         <v>2.0536732762728639E-2</v>
@@ -4289,7 +4289,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D62">
         <v>2.0536732762728639E-2</v>
@@ -4342,7 +4342,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D63">
         <v>2.145302635453868E-2</v>
@@ -4395,7 +4395,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D64">
         <v>2.145302635453868E-2</v>
@@ -4448,7 +4448,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D65">
         <v>2.145302635453868E-2</v>
@@ -4501,7 +4501,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D66">
         <v>2.9645217128281689E-2</v>
@@ -4554,7 +4554,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D67">
         <v>0.26648296391625759</v>
@@ -4607,7 +4607,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D68">
         <v>0.90308858817890503</v>
@@ -4660,7 +4660,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D69">
         <v>0.90308858817890503</v>
@@ -4713,7 +4713,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D70">
         <v>0.90308858817890503</v>
@@ -4766,7 +4766,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D71">
         <v>0.90308858817890503</v>
@@ -4819,7 +4819,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D72">
         <v>0.90308858817890503</v>
@@ -4872,7 +4872,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D73">
         <v>0.90308858817890503</v>
@@ -4925,7 +4925,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D74">
         <v>0.90308858817890503</v>
@@ -4978,7 +4978,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D75">
         <v>0.90308858817890503</v>
@@ -5031,7 +5031,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D76">
         <v>0.90308858817890503</v>
@@ -5084,7 +5084,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D77">
         <v>0.90308858817890503</v>
@@ -5137,7 +5137,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D78">
         <v>0.90308858817890503</v>
@@ -5190,7 +5190,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D79">
         <v>0.90308858817890503</v>
@@ -5243,7 +5243,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D80">
         <v>0.90308858817890503</v>
@@ -5296,7 +5296,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D81">
         <v>0.90308858817890503</v>
@@ -5349,7 +5349,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D82">
         <v>0.90308858817890503</v>
@@ -5402,7 +5402,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D83">
         <v>0.90308858817890503</v>
@@ -5455,7 +5455,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D84">
         <v>0.99160999103513592</v>
@@ -5508,7 +5508,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D85">
         <v>0.99160999103513592</v>
@@ -5561,7 +5561,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D86">
         <v>0.99160999103513592</v>
@@ -5614,7 +5614,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D87">
         <v>0.99160999103513592</v>
@@ -5667,7 +5667,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88">
         <v>0.99160999103513592</v>
@@ -5720,7 +5720,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D89">
         <v>0.99160999103513592</v>
@@ -5773,7 +5773,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D90">
         <v>0.99160999103513592</v>
@@ -5826,7 +5826,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D91">
         <v>0.99160999103513592</v>
@@ -5879,7 +5879,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D92">
         <v>0.99160999103513592</v>
@@ -5932,7 +5932,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D93">
         <v>0.99160999103513592</v>
@@ -5985,7 +5985,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D94">
         <v>0.99160999103513592</v>
@@ -6038,7 +6038,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D95">
         <v>0.99160999103513592</v>
@@ -6091,7 +6091,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D96">
         <v>0.99160999103513592</v>
@@ -6144,7 +6144,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D97">
         <v>0.99160999103513592</v>
@@ -6197,7 +6197,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D98">
         <v>0.99160999103513592</v>
@@ -6250,7 +6250,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D99">
         <v>0.99160999103513592</v>
@@ -6303,7 +6303,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D100">
         <v>0.99160999103513592</v>
@@ -6356,7 +6356,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D101">
         <v>0.99160999103513592</v>
@@ -6409,7 +6409,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D102">
         <v>0.99160999103513592</v>
@@ -6462,7 +6462,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D103">
         <v>0.99160999103513592</v>
@@ -6515,7 +6515,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D104">
         <v>0.99160999103513592</v>
@@ -6568,7 +6568,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D105">
         <v>0.99160999103513592</v>
@@ -6621,7 +6621,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D106">
         <v>0.99160999103513592</v>
@@ -6674,7 +6674,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D107">
         <v>0.99160999103513592</v>
@@ -6727,7 +6727,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D108">
         <v>0.99160999103513592</v>
@@ -6780,7 +6780,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D109">
         <v>0.99160999103513592</v>
@@ -6833,7 +6833,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D110">
         <v>0.99160999103513592</v>
@@ -6886,7 +6886,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D111">
         <v>0.99160999103513592</v>
@@ -6939,7 +6939,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D112">
         <v>0.99160999103513592</v>
@@ -6992,7 +6992,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D113">
         <v>0.99160999103513592</v>
@@ -7045,7 +7045,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D114">
         <v>0.99160999103513592</v>
@@ -7098,7 +7098,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D115">
         <v>0.99160999103513592</v>
@@ -7151,7 +7151,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D116">
         <v>0.99160999103513592</v>
@@ -7204,7 +7204,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D117">
         <v>0.99160999103513592</v>
@@ -7257,7 +7257,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D118">
         <v>0.99160999103513592</v>
@@ -7310,7 +7310,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D119">
         <v>0.99160999103513592</v>
@@ -7363,7 +7363,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D120">
         <v>0.99160999103513592</v>
@@ -7416,7 +7416,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D121">
         <v>0.99160999103513592</v>
@@ -13631,7 +13631,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
